--- a/artfynd/A 969-2024 artfynd.xlsx
+++ b/artfynd/A 969-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 969-2024 artfynd.xlsx
+++ b/artfynd/A 969-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4168039</v>
+        <v>4214684</v>
       </c>
       <c r="B2" t="n">
-        <v>95510</v>
+        <v>95518</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4214684</v>
+        <v>89274543</v>
       </c>
       <c r="B3" t="n">
-        <v>95518</v>
+        <v>95519</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,17 +828,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergbrant ca 250 m SSV om torpet BJÖRNEMYREN, Boh</t>
+          <t>Cirka 250 m SSV om torpet BJÖRNEMYREN, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>332263.3528618161</v>
+        <v>332268.3022065568</v>
       </c>
       <c r="R3" t="n">
-        <v>6474396.0104701</v>
+        <v>6474401.049921738</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,6 +878,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bohusläns flora - 2011.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,269 +896,21 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>klippstup</t>
+          <t>Bergbrant, klippstup</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
+          <t>Evastina Blomgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>89274543</v>
-      </c>
-      <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Cirka 250 m SSV om torpet BJÖRNEMYREN, Boh</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>332268.3022065568</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6474401.049921738</v>
-      </c>
-      <c r="S4" t="n">
-        <v>100</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Uddevalla</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Lane-Ryr</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>1999-05-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>1999-05-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bohusläns flora - 2011.</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Bergbrant, klippstup</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Evastina Blomgren</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
           <t>Hans Alexandersson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Bohusläns Flora 2011</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>89274554</v>
-      </c>
-      <c r="B5" t="n">
-        <v>95511</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>221944</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Lopplummer</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Huperzia selago</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Cirka 250 m SSV om torpet BJÖRNEMYREN, Boh</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>332268.3022065568</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6474401.049921738</v>
-      </c>
-      <c r="S5" t="n">
-        <v>100</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Uddevalla</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Lane-Ryr</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>1999-05-30</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>1999-05-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bohusläns flora - 2011.</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Bergbrant, klippstup</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Evastina Blomgren</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Hans Alexandersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Bohusläns Flora 2011</t>
         </is>

--- a/artfynd/A 969-2024 artfynd.xlsx
+++ b/artfynd/A 969-2024 artfynd.xlsx
@@ -795,12 +795,7 @@
         <v>89274543</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>332268.3022065568</v>
+        <v>332268</v>
       </c>
       <c r="R3" t="n">
-        <v>6474401.049921738</v>
+        <v>6474401</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -865,19 +860,9 @@
           <t>1999-05-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1999-05-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 969-2024 artfynd.xlsx
+++ b/artfynd/A 969-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>89274543</v>
       </c>
       <c r="B3" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 969-2024 artfynd.xlsx
+++ b/artfynd/A 969-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>89274543</v>
       </c>
       <c r="B3" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 969-2024 artfynd.xlsx
+++ b/artfynd/A 969-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>89274543</v>
       </c>
       <c r="B3" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 969-2024 artfynd.xlsx
+++ b/artfynd/A 969-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>89274543</v>
       </c>
       <c r="B3" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 969-2024 artfynd.xlsx
+++ b/artfynd/A 969-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>89274543</v>
       </c>
       <c r="B3" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 969-2024 artfynd.xlsx
+++ b/artfynd/A 969-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>89274543</v>
       </c>
       <c r="B3" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 969-2024 artfynd.xlsx
+++ b/artfynd/A 969-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>89274543</v>
       </c>
       <c r="B3" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 969-2024 artfynd.xlsx
+++ b/artfynd/A 969-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4214684</v>
+        <v>4168039</v>
       </c>
       <c r="B2" t="n">
-        <v>95518</v>
+        <v>95510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -792,10 +792,15 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89274543</v>
+        <v>4214684</v>
       </c>
       <c r="B3" t="n">
-        <v>97522</v>
+        <v>95518</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,17 +828,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Cirka 250 m SSV om torpet BJÖRNEMYREN, Boh</t>
+          <t>Bergbrant ca 250 m SSV om torpet BJÖRNEMYREN, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>332268</v>
+        <v>332263.3528618161</v>
       </c>
       <c r="R3" t="n">
-        <v>6474401</v>
+        <v>6474396.0104701</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,14 +865,19 @@
           <t>1999-05-30</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1999-05-30</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bohusläns flora - 2011.</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,21 +891,235 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Bergbrant, klippstup</t>
+          <t>klippstup</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Föreningen Bohusläns Flora</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Föreningen Bohusläns Flora</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>89274543</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97522</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Cirka 250 m SSV om torpet BJÖRNEMYREN, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>332268</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6474401</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lane-Ryr</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1999-05-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1999-05-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bohusläns flora - 2011.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Bergbrant, klippstup</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Evastina Blomgren</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Hans Alexandersson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Bohusläns Flora 2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>89274554</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97516</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Cirka 250 m SSV om torpet BJÖRNEMYREN, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>332268</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6474401</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lane-Ryr</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1999-05-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1999-05-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bohusläns flora - 2011.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Bergbrant, klippstup</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Evastina Blomgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hans Alexandersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Bohusläns Flora 2011</t>
         </is>
